--- a/División/UOcc_División.xlsx
+++ b/División/UOcc_División.xlsx
@@ -428,16 +428,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>52.79998842192862</v>
+        <v>52.79998842192865</v>
       </c>
       <c r="C2" s="2">
-        <v>115.7375475785795</v>
+        <v>115.7385888621269</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>61.1094117213141</v>
+        <v>61.10996151890659</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -445,7 +445,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>18.74713032440267</v>
+        <v>18.74713032440266</v>
       </c>
       <c r="C3" s="2">
         <v>110.1457256168668</v>
@@ -454,7 +454,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="2">
-        <v>20.649162728153</v>
+        <v>20.64916272815299</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -462,7 +462,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>14.0554939592237</v>
+        <v>14.05549395922371</v>
       </c>
       <c r="C4" s="2">
         <v>117.0895973034999</v>
